--- a/Result/profitability/5608.xlsx
+++ b/Result/profitability/5608.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.53</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2625</v>
+        <v>0.29</v>
       </c>
       <c r="N2" t="n">
-        <v>13.82</v>
+        <v>15.1075</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.52</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4275</v>
+        <v>0.53</v>
       </c>
       <c r="N3" t="n">
-        <v>19.5225</v>
+        <v>20.985</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>6.07</v>
       </c>
       <c r="M4" t="n">
-        <v>1.23625</v>
+        <v>1.34625</v>
       </c>
       <c r="N4" t="n">
-        <v>25.03125</v>
+        <v>28.76375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.51</v>
       </c>
       <c r="M5" t="n">
-        <v>1.4825</v>
+        <v>1.465</v>
       </c>
       <c r="N5" t="n">
-        <v>31.3</v>
+        <v>34.09125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.14</v>
       </c>
       <c r="M6" t="n">
-        <v>1.555</v>
+        <v>1.63625</v>
       </c>
       <c r="N6" t="n">
-        <v>36.00875</v>
+        <v>37.7025</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.9</v>
       </c>
       <c r="M7" t="n">
-        <v>1.69625</v>
+        <v>1.7475</v>
       </c>
       <c r="N7" t="n">
-        <v>40.58875</v>
+        <v>41.62</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>1.78125</v>
+        <v>1.8475</v>
       </c>
       <c r="N8" t="n">
-        <v>43.1925</v>
+        <v>44.8325</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1415,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
         <v>98.3</v>
@@ -1775,7 +1775,7 @@
         <v>1.58125</v>
       </c>
       <c r="N11" t="n">
-        <v>43.3575</v>
+        <v>43.35749999999999</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1902,7 +1902,7 @@
         <v>0.9350000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>41.33000000000001</v>
+        <v>41.33</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2026,7 +2026,7 @@
         <v>0.68</v>
       </c>
       <c r="M13" t="n">
-        <v>0.83125</v>
+        <v>0.8312500000000002</v>
       </c>
       <c r="N13" t="n">
         <v>41.325</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5608</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>853</v>
+      </c>
+      <c r="D75" t="n">
+        <v>643</v>
+      </c>
+      <c r="E75" t="n">
+        <v>210</v>
+      </c>
+      <c r="F75" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="G75" t="n">
+        <v>132</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>15.46%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>11</v>
+      </c>
+      <c r="J75" t="n">
+        <v>143</v>
+      </c>
+      <c r="K75" t="n">
+        <v>165</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.001250000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>11.00125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-4.818181818181818</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>1.138888888888889</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.1400000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.2500000000000001</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>22.33</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>9.666666666666666</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
